--- a/MintSheets_Gumroad_Launch/XLSX_Templates/HVAC_Air_Balance_Report_Template/HVAC_Air_Balance_Report_Template.xlsx
+++ b/MintSheets_Gumroad_Launch/XLSX_Templates/HVAC_Air_Balance_Report_Template/HVAC_Air_Balance_Report_Template.xlsx
@@ -1,34 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Supply Air Balance" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Return &amp; Exhaust Air" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="AHU-RTU Performance" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Static Pressure Traverse" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Hydronic Balance" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Commissioning Checklist" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Deficiency Log" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Summary &amp; Sign-Off" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Supply Air Balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Return &amp; Exhaust Air" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AHU-RTU Performance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Static Pressure Traverse" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hydronic Balance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Commissioning Checklist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Deficiency Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary &amp; Sign-Off" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <si>
     <t xml:space="preserve">Your HVAC Co.</t>
   </si>
@@ -75,7 +72,7 @@
     <t xml:space="preserve">Owner Phone / Email:</t>
   </si>
   <si>
-    <t xml:space="preserve">Company:</t>
+    <t>Company:</t>
   </si>
   <si>
     <t xml:space="preserve">  ⚙️  SYSTEM INFORMATION</t>
@@ -168,13 +165,13 @@
     <t xml:space="preserve">Certified Test &amp; Balance Technician:</t>
   </si>
   <si>
-    <t xml:space="preserve">Signature:</t>
+    <t>Signature:</t>
   </si>
   <si>
     <t xml:space="preserve">NEBB / AABC Certification #:</t>
   </si>
   <si>
-    <t xml:space="preserve">Date:</t>
+    <t>Date:</t>
   </si>
   <si>
     <t xml:space="preserve">Engineer of Record:</t>
@@ -222,73 +219,73 @@
     <t xml:space="preserve">Ak Factor</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diffuser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-20</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>SA-01</t>
+  </si>
+  <si>
+    <t>Diffuser</t>
+  </si>
+  <si>
+    <t>SA-02</t>
+  </si>
+  <si>
+    <t>SA-03</t>
+  </si>
+  <si>
+    <t>SA-04</t>
+  </si>
+  <si>
+    <t>SA-05</t>
+  </si>
+  <si>
+    <t>SA-06</t>
+  </si>
+  <si>
+    <t>SA-07</t>
+  </si>
+  <si>
+    <t>SA-08</t>
+  </si>
+  <si>
+    <t>SA-09</t>
+  </si>
+  <si>
+    <t>SA-10</t>
+  </si>
+  <si>
+    <t>SA-11</t>
+  </si>
+  <si>
+    <t>SA-12</t>
+  </si>
+  <si>
+    <t>SA-13</t>
+  </si>
+  <si>
+    <t>SA-14</t>
+  </si>
+  <si>
+    <t>SA-15</t>
+  </si>
+  <si>
+    <t>SA-16</t>
+  </si>
+  <si>
+    <t>SA-17</t>
+  </si>
+  <si>
+    <t>SA-18</t>
+  </si>
+  <si>
+    <t>SA-19</t>
+  </si>
+  <si>
+    <t>SA-20</t>
   </si>
   <si>
     <t xml:space="preserve">SYSTEM TOTALS</t>
@@ -309,7 +306,7 @@
     <t xml:space="preserve">Balance Tolerance (±10%):</t>
   </si>
   <si>
-    <t xml:space="preserve">±10%</t>
+    <t>±10%</t>
   </si>
   <si>
     <t xml:space="preserve">Number of Outlets:</t>
@@ -330,40 +327,40 @@
     <t xml:space="preserve">Grille Size</t>
   </si>
   <si>
-    <t xml:space="preserve">RA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RA-12</t>
+    <t>RA-01</t>
+  </si>
+  <si>
+    <t>RA-02</t>
+  </si>
+  <si>
+    <t>RA-03</t>
+  </si>
+  <si>
+    <t>RA-04</t>
+  </si>
+  <si>
+    <t>RA-05</t>
+  </si>
+  <si>
+    <t>RA-06</t>
+  </si>
+  <si>
+    <t>RA-07</t>
+  </si>
+  <si>
+    <t>RA-08</t>
+  </si>
+  <si>
+    <t>RA-09</t>
+  </si>
+  <si>
+    <t>RA-10</t>
+  </si>
+  <si>
+    <t>RA-11</t>
+  </si>
+  <si>
+    <t>RA-12</t>
   </si>
   <si>
     <t xml:space="preserve">RETURN TOTALS</t>
@@ -390,28 +387,28 @@
     <t xml:space="preserve">Amp Draw</t>
   </si>
   <si>
-    <t xml:space="preserve">EX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-08</t>
+    <t>EX-01</t>
+  </si>
+  <si>
+    <t>EX-02</t>
+  </si>
+  <si>
+    <t>EX-03</t>
+  </si>
+  <si>
+    <t>EX-04</t>
+  </si>
+  <si>
+    <t>EX-05</t>
+  </si>
+  <si>
+    <t>EX-06</t>
+  </si>
+  <si>
+    <t>EX-07</t>
+  </si>
+  <si>
+    <t>EX-08</t>
   </si>
   <si>
     <t xml:space="preserve">EXHAUST TOTALS</t>
@@ -420,7 +417,7 @@
     <t xml:space="preserve">  🏭  AIR HANDLING UNIT / RTU PERFORMANCE DATA</t>
   </si>
   <si>
-    <t xml:space="preserve">Parameter</t>
+    <t>Parameter</t>
   </si>
   <si>
     <t xml:space="preserve">Design / Spec</t>
@@ -429,16 +426,16 @@
     <t xml:space="preserve">Measured Value</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolerance</t>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Tolerance</t>
   </si>
   <si>
     <t xml:space="preserve">Total Supply CFM</t>
   </si>
   <si>
-    <t xml:space="preserve">CFM</t>
+    <t>CFM</t>
   </si>
   <si>
     <t xml:space="preserve">Total Return CFM</t>
@@ -453,7 +450,7 @@
     <t xml:space="preserve">in. wg</t>
   </si>
   <si>
-    <t xml:space="preserve">±0.1</t>
+    <t>±0.1</t>
   </si>
   <si>
     <t xml:space="preserve">Return Static Pressure</t>
@@ -465,10 +462,10 @@
     <t xml:space="preserve">Fan RPM (Design)</t>
   </si>
   <si>
-    <t xml:space="preserve">RPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±5%</t>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>±5%</t>
   </si>
   <si>
     <t xml:space="preserve">Fan RPM (Measured)</t>
@@ -477,19 +474,19 @@
     <t xml:space="preserve">Motor Full Load Amps (FLA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Amps</t>
+    <t>Amps</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Measured Amps</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;FLA</t>
+    <t>&lt;FLA</t>
   </si>
   <si>
     <t xml:space="preserve">Supply Fan Motor HP</t>
   </si>
   <si>
-    <t xml:space="preserve">HP</t>
+    <t>HP</t>
   </si>
   <si>
     <t xml:space="preserve">Drive Belt Size / Sheave</t>
@@ -498,7 +495,7 @@
     <t xml:space="preserve">Entering Air Temp (Dry Bulb)</t>
   </si>
   <si>
-    <t xml:space="preserve">°F</t>
+    <t>°F</t>
   </si>
   <si>
     <t xml:space="preserve">Leaving Air Temp (Dry Bulb)</t>
@@ -525,7 +522,7 @@
     <t xml:space="preserve">Economizer Damper Position (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">%</t>
+    <t>%</t>
   </si>
   <si>
     <t xml:space="preserve">OSA Damper Position (%)</t>
@@ -540,13 +537,13 @@
     <t xml:space="preserve">Coil Parameter</t>
   </si>
   <si>
-    <t xml:space="preserve">Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance</t>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Measured</t>
+  </si>
+  <si>
+    <t>Variance</t>
   </si>
   <si>
     <t xml:space="preserve">Cooling Coil — EAT (DB)</t>
@@ -609,49 +606,49 @@
     <t xml:space="preserve">TP (in. wg)</t>
   </si>
   <si>
-    <t xml:space="preserve">DUCT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCT-15</t>
+    <t>DUCT-01</t>
+  </si>
+  <si>
+    <t>DUCT-02</t>
+  </si>
+  <si>
+    <t>DUCT-03</t>
+  </si>
+  <si>
+    <t>DUCT-04</t>
+  </si>
+  <si>
+    <t>DUCT-05</t>
+  </si>
+  <si>
+    <t>DUCT-06</t>
+  </si>
+  <si>
+    <t>DUCT-07</t>
+  </si>
+  <si>
+    <t>DUCT-08</t>
+  </si>
+  <si>
+    <t>DUCT-09</t>
+  </si>
+  <si>
+    <t>DUCT-10</t>
+  </si>
+  <si>
+    <t>DUCT-11</t>
+  </si>
+  <si>
+    <t>DUCT-12</t>
+  </si>
+  <si>
+    <t>DUCT-13</t>
+  </si>
+  <si>
+    <t>DUCT-14</t>
+  </si>
+  <si>
+    <t>DUCT-15</t>
   </si>
   <si>
     <t xml:space="preserve">  💧  HYDRONIC SYSTEM BALANCE — FLOW MEASUREMENTS</t>
@@ -681,52 +678,52 @@
     <t xml:space="preserve">Meas. ∆P (ft)</t>
   </si>
   <si>
-    <t xml:space="preserve">HYD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYD-16</t>
+    <t>HYD-01</t>
+  </si>
+  <si>
+    <t>HYD-02</t>
+  </si>
+  <si>
+    <t>HYD-03</t>
+  </si>
+  <si>
+    <t>HYD-04</t>
+  </si>
+  <si>
+    <t>HYD-05</t>
+  </si>
+  <si>
+    <t>HYD-06</t>
+  </si>
+  <si>
+    <t>HYD-07</t>
+  </si>
+  <si>
+    <t>HYD-08</t>
+  </si>
+  <si>
+    <t>HYD-09</t>
+  </si>
+  <si>
+    <t>HYD-10</t>
+  </si>
+  <si>
+    <t>HYD-11</t>
+  </si>
+  <si>
+    <t>HYD-12</t>
+  </si>
+  <si>
+    <t>HYD-13</t>
+  </si>
+  <si>
+    <t>HYD-14</t>
+  </si>
+  <si>
+    <t>HYD-15</t>
+  </si>
+  <si>
+    <t>HYD-16</t>
   </si>
   <si>
     <t xml:space="preserve">  ☑️  PRE-TEST &amp; COMMISSIONING CHECKLIST</t>
@@ -735,13 +732,13 @@
     <t xml:space="preserve">Checklist Item</t>
   </si>
   <si>
-    <t xml:space="preserve">Pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t xml:space="preserve">Notes / Corrective Action</t>
@@ -753,7 +750,7 @@
     <t xml:space="preserve">   All ductwork installed and sealed per design drawings</t>
   </si>
   <si>
-    <t xml:space="preserve">☐</t>
+    <t>☐</t>
   </si>
   <si>
     <t xml:space="preserve">   All grilles, registers, and diffusers installed and unobstructed</t>
@@ -870,7 +867,7 @@
     <t xml:space="preserve">  ⚠️  DEFICIENCY LOG &amp; CORRECTIVE ACTION TRACKING</t>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
+    <t>#</t>
   </si>
   <si>
     <t xml:space="preserve">Location / System</t>
@@ -912,7 +909,7 @@
     <t xml:space="preserve">  📊  SYSTEM BALANCE RESULTS SUMMARY</t>
   </si>
   <si>
-    <t xml:space="preserve">System</t>
+    <t>System</t>
   </si>
   <si>
     <t xml:space="preserve"># Outlets</t>
@@ -975,7 +972,7 @@
     <t xml:space="preserve">Expiration Date:</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone:</t>
+    <t>Phone:</t>
   </si>
   <si>
     <t xml:space="preserve">License #:</t>
@@ -987,7 +984,7 @@
     <t xml:space="preserve">Owner Representative:</t>
   </si>
   <si>
-    <t xml:space="preserve">Title:</t>
+    <t>Title:</t>
   </si>
   <si>
     <t xml:space="preserve">Date Accepted:</t>
@@ -996,147 +993,102 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="14.000000"/>
+      <color indexed="65"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12.000000"/>
+      <color indexed="65"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
+      <b/>
+      <sz val="20.000000"/>
+      <color rgb="FF1B3A6B"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <b/>
+      <sz val="11.000000"/>
+      <color indexed="65"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="20"/>
+      <b/>
+      <sz val="9.000000"/>
       <color rgb="FF1B3A6B"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9.000000"/>
+      <color indexed="4"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="9"/>
+      <i/>
+      <sz val="8.000000"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.000000"/>
+      <color indexed="65"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color indexed="65"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.000000"/>
+      <color indexed="4"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.000000"/>
+      <color indexed="64"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16.000000"/>
       <color rgb="FF1B3A6B"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF1B3A6B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1149,13 +1101,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1B3A6B"/>
-        <bgColor rgb="FF333399"/>
+        <bgColor indexed="62"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE07B00"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor indexed="52"/>
       </patternFill>
     </fill>
     <fill>
@@ -1173,31 +1125,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6F8"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E6DA4"/>
-        <bgColor rgb="FF3366FF"/>
+        <bgColor indexed="48"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor indexed="65"/>
         <bgColor rgb="FFF4F6F8"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1210,296 +1162,222 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="thin">
         <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="4" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="5" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="6" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="7" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="7" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="8" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="9" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="7" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="8" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="11" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="6" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="11" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="12" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="12" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="13" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="13" fillId="5" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="14" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="14" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="12" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="12" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="15" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="10" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="7" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="16" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="7" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFD6E4F0"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2E6DA4"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF4F6F8"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFE07B00"/>
-      <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1B3A6B"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1507,17 +1385,300 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1541,7 +1702,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1562,7 +1722,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1610,10 +1769,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:path path="circle"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1628,30 +1784,28 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="22"/>
+    <col customWidth="1" min="2" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1669,8 +1823,8 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="7.5" customHeight="1"/>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1686,8 +1840,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="4.5" customHeight="1"/>
+    <row r="5" ht="21.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1702,118 +1856,117 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" ht="4.5" customHeight="1"/>
+    <row r="13" ht="21.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
@@ -1828,155 +1981,153 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="6" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="6" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="6" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="6" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="6" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" ht="4.5" customHeight="1"/>
+    <row r="23" ht="21.75" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -1991,102 +2142,99 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="6" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="6" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="6" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="6" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="6" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" ht="4.5" customHeight="1"/>
+    <row r="30" ht="21.75" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>44</v>
       </c>
@@ -2101,99 +2249,95 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="6" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="6" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="6" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="6" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" ht="4.5" customHeight="1"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2206,31 +2350,28 @@
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A36:L36"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="18"/>
+    <col customWidth="1" min="2" max="9" style="0" width="12"/>
+    <col customWidth="1" min="10" max="11" style="0" width="10"/>
+    <col customWidth="1" min="12" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2239,14 +2380,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>53</v>
       </c>
@@ -2261,9 +2402,9 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>54</v>
       </c>
@@ -2301,7 +2442,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
@@ -2312,7 +2453,7 @@
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="14" t="str">
-        <f aca="false">IF(D4&gt;0,E4/D4*100,"")</f>
+        <f t="shared" ref="F4:F9" si="0">IF(D4&gt;0,E4/D4*100,"")</f>
         <v/>
       </c>
       <c r="G4" s="13"/>
@@ -2320,12 +2461,12 @@
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="15" t="str">
-        <f aca="false">IF(F4="","",IF(AND(F4&gt;=90,F4&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K4:K9" si="1">IF(F4="","",IF(AND(F4&gt;=90,F4&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>68</v>
       </c>
@@ -2336,7 +2477,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="17" t="str">
-        <f aca="false">IF(D5&gt;0,E5/D5*100,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G5" s="13"/>
@@ -2344,12 +2485,12 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
       <c r="K5" s="18" t="str">
-        <f aca="false">IF(F5="","",IF(AND(F5&gt;=90,F5&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>69</v>
       </c>
@@ -2360,7 +2501,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14" t="str">
-        <f aca="false">IF(D6&gt;0,E6/D6*100,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G6" s="13"/>
@@ -2368,12 +2509,12 @@
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
       <c r="K6" s="15" t="str">
-        <f aca="false">IF(F6="","",IF(AND(F6&gt;=90,F6&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>70</v>
       </c>
@@ -2384,7 +2525,7 @@
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="17" t="str">
-        <f aca="false">IF(D7&gt;0,E7/D7*100,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G7" s="13"/>
@@ -2392,12 +2533,12 @@
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
       <c r="K7" s="18" t="str">
-        <f aca="false">IF(F7="","",IF(AND(F7&gt;=90,F7&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>71</v>
       </c>
@@ -2408,7 +2549,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="14" t="str">
-        <f aca="false">IF(D8&gt;0,E8/D8*100,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G8" s="13"/>
@@ -2416,12 +2557,12 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="15" t="str">
-        <f aca="false">IF(F8="","",IF(AND(F8&gt;=90,F8&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>72</v>
       </c>
@@ -2432,7 +2573,7 @@
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17" t="str">
-        <f aca="false">IF(D9&gt;0,E9/D9*100,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G9" s="13"/>
@@ -2440,12 +2581,12 @@
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
       <c r="K9" s="18" t="str">
-        <f aca="false">IF(F9="","",IF(AND(F9&gt;=90,F9&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L9" s="16"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>73</v>
       </c>
@@ -2456,7 +2597,7 @@
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="14" t="str">
-        <f aca="false">IF(D10&gt;0,E10/D10*100,"")</f>
+        <f t="shared" ref="F10:F24" si="2">IF(D10&gt;0,E10/D10*100,"")</f>
         <v/>
       </c>
       <c r="G10" s="13"/>
@@ -2464,12 +2605,12 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="15" t="str">
-        <f aca="false">IF(F10="","",IF(AND(F10&gt;=90,F10&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K10:K23" si="3">IF(F10="","",IF(AND(F10&gt;=90,F10&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>74</v>
       </c>
@@ -2480,7 +2621,7 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="17" t="str">
-        <f aca="false">IF(D11&gt;0,E11/D11*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G11" s="13"/>
@@ -2488,12 +2629,12 @@
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
       <c r="K11" s="18" t="str">
-        <f aca="false">IF(F11="","",IF(AND(F11&gt;=90,F11&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L11" s="16"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>75</v>
       </c>
@@ -2504,7 +2645,7 @@
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="14" t="str">
-        <f aca="false">IF(D12&gt;0,E12/D12*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G12" s="13"/>
@@ -2512,12 +2653,12 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="15" t="str">
-        <f aca="false">IF(F12="","",IF(AND(F12&gt;=90,F12&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>76</v>
       </c>
@@ -2528,7 +2669,7 @@
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="17" t="str">
-        <f aca="false">IF(D13&gt;0,E13/D13*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G13" s="13"/>
@@ -2536,12 +2677,12 @@
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="18" t="str">
-        <f aca="false">IF(F13="","",IF(AND(F13&gt;=90,F13&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>77</v>
       </c>
@@ -2552,7 +2693,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="14" t="str">
-        <f aca="false">IF(D14&gt;0,E14/D14*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G14" s="13"/>
@@ -2560,12 +2701,12 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="15" t="str">
-        <f aca="false">IF(F14="","",IF(AND(F14&gt;=90,F14&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>78</v>
       </c>
@@ -2576,7 +2717,7 @@
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="17" t="str">
-        <f aca="false">IF(D15&gt;0,E15/D15*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G15" s="13"/>
@@ -2584,12 +2725,12 @@
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="18" t="str">
-        <f aca="false">IF(F15="","",IF(AND(F15&gt;=90,F15&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="s">
         <v>79</v>
       </c>
@@ -2600,7 +2741,7 @@
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="14" t="str">
-        <f aca="false">IF(D16&gt;0,E16/D16*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G16" s="13"/>
@@ -2608,12 +2749,12 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
       <c r="K16" s="15" t="str">
-        <f aca="false">IF(F16="","",IF(AND(F16&gt;=90,F16&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="s">
         <v>80</v>
       </c>
@@ -2624,7 +2765,7 @@
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="17" t="str">
-        <f aca="false">IF(D17&gt;0,E17/D17*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G17" s="13"/>
@@ -2632,12 +2773,12 @@
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
       <c r="K17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(AND(F17&gt;=90,F17&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="s">
         <v>81</v>
       </c>
@@ -2648,7 +2789,7 @@
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14" t="str">
-        <f aca="false">IF(D18&gt;0,E18/D18*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G18" s="13"/>
@@ -2656,12 +2797,12 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="15" t="str">
-        <f aca="false">IF(F18="","",IF(AND(F18&gt;=90,F18&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
         <v>82</v>
       </c>
@@ -2672,7 +2813,7 @@
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="17" t="str">
-        <f aca="false">IF(D19&gt;0,E19/D19*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G19" s="13"/>
@@ -2680,12 +2821,12 @@
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
       <c r="K19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(AND(F19&gt;=90,F19&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12" t="s">
         <v>83</v>
       </c>
@@ -2696,7 +2837,7 @@
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="14" t="str">
-        <f aca="false">IF(D20&gt;0,E20/D20*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G20" s="13"/>
@@ -2704,12 +2845,12 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="15" t="str">
-        <f aca="false">IF(F20="","",IF(AND(F20&gt;=90,F20&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>84</v>
       </c>
@@ -2720,7 +2861,7 @@
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="17" t="str">
-        <f aca="false">IF(D21&gt;0,E21/D21*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G21" s="13"/>
@@ -2728,12 +2869,12 @@
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
       <c r="K21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(AND(F21&gt;=90,F21&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L21" s="16"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="12" t="s">
         <v>85</v>
       </c>
@@ -2744,7 +2885,7 @@
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="14" t="str">
-        <f aca="false">IF(D22&gt;0,E22/D22*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G22" s="13"/>
@@ -2752,12 +2893,12 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="15" t="str">
-        <f aca="false">IF(F22="","",IF(AND(F22&gt;=90,F22&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
         <v>86</v>
       </c>
@@ -2768,7 +2909,7 @@
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="17" t="str">
-        <f aca="false">IF(D23&gt;0,E23/D23*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G23" s="13"/>
@@ -2776,27 +2917,27 @@
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
       <c r="K23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(AND(F23&gt;=90,F23&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L23" s="16"/>
     </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="19" t="s">
         <v>87</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
-      <c r="D24" s="19" t="n">
-        <f aca="false">SUM(D4:D23)</f>
+      <c r="D24" s="19">
+        <f>SUM(D4:D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="19" t="n">
-        <f aca="false">SUM(E4:E23)</f>
+      <c r="E24" s="19">
+        <f>SUM(E4:E23)</f>
         <v>0</v>
       </c>
       <c r="F24" s="20" t="str">
-        <f aca="false">IF(D24&gt;0,E24/D24*100,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G24" s="19"/>
@@ -2806,8 +2947,8 @@
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="4.5" customHeight="1"/>
+    <row r="26" ht="21.75" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>88</v>
       </c>
@@ -2822,26 +2963,26 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="21" t="n">
-        <f aca="false">D24</f>
+      <c r="B27" s="21">
+        <f>D24</f>
         <v>0</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="21" t="n">
-        <f aca="false">E24</f>
+      <c r="H27" s="21">
+        <f>E24</f>
         <v>0</v>
       </c>
       <c r="I27" s="22"/>
@@ -2849,19 +2990,19 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B28" s="23" t="str">
-        <f aca="false">IF(D24&gt;0,E24/D24*100,"")</f>
+        <f>IF(D24&gt;0,E24/D24*100,"")</f>
         <v/>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H28" s="21" t="s">
@@ -2872,46 +3013,46 @@
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="21" t="n">
-        <f aca="false">COUNTA(A4:A23)</f>
+      <c r="B29" s="21">
+        <f>COUNTA(A4:A23)</f>
         <v>20</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>95</v>
       </c>
       <c r="H29" s="21" t="str">
-        <f aca="false">IF(AND(F24&gt;=90,F24&lt;=110),"✓ BALANCED","✗ REBALANCE REQUIRED")</f>
-        <v>✗ REBALANCE REQUIRED</v>
+        <f>IF(AND(F24&gt;=90,F24&lt;=110),"✓ BALANCED","✗ REBALANCE REQUIRED")</f>
+        <v xml:space="preserve">✗ REBALANCE REQUIRED</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+    <row r="30" ht="4.5" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2921,31 +3062,28 @@
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A31:L31"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="18"/>
+    <col customWidth="1" min="2" max="9" style="0" width="12"/>
+    <col customWidth="1" min="10" max="11" style="0" width="10"/>
+    <col customWidth="1" min="12" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2954,14 +3092,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>96</v>
       </c>
@@ -2976,9 +3114,8 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>97</v>
       </c>
@@ -3016,7 +3153,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>100</v>
       </c>
@@ -3025,7 +3162,7 @@
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="25" t="str">
-        <f aca="false">IF(D4&gt;0,E4/D4*100,"")</f>
+        <f t="shared" ref="F4:F9" si="4">IF(D4&gt;0,E4/D4*100,"")</f>
         <v/>
       </c>
       <c r="G4" s="13"/>
@@ -3033,12 +3170,12 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="15" t="str">
-        <f aca="false">IF(F4="","",IF(AND(F4&gt;=90,F4&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K4:K9" si="5">IF(F4="","",IF(AND(F4&gt;=90,F4&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L4" s="25"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>101</v>
       </c>
@@ -3047,7 +3184,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="26" t="str">
-        <f aca="false">IF(D5&gt;0,E5/D5*100,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G5" s="13"/>
@@ -3055,12 +3192,12 @@
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>
       <c r="K5" s="18" t="str">
-        <f aca="false">IF(F5="","",IF(AND(F5&gt;=90,F5&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>102</v>
       </c>
@@ -3069,7 +3206,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="25" t="str">
-        <f aca="false">IF(D6&gt;0,E6/D6*100,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G6" s="13"/>
@@ -3077,12 +3214,12 @@
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="15" t="str">
-        <f aca="false">IF(F6="","",IF(AND(F6&gt;=90,F6&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>103</v>
       </c>
@@ -3091,7 +3228,7 @@
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26" t="str">
-        <f aca="false">IF(D7&gt;0,E7/D7*100,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G7" s="13"/>
@@ -3099,12 +3236,12 @@
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
       <c r="K7" s="18" t="str">
-        <f aca="false">IF(F7="","",IF(AND(F7&gt;=90,F7&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>104</v>
       </c>
@@ -3113,7 +3250,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="25" t="str">
-        <f aca="false">IF(D8&gt;0,E8/D8*100,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G8" s="13"/>
@@ -3121,12 +3258,12 @@
       <c r="I8" s="25"/>
       <c r="J8" s="25"/>
       <c r="K8" s="15" t="str">
-        <f aca="false">IF(F8="","",IF(AND(F8&gt;=90,F8&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L8" s="25"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>105</v>
       </c>
@@ -3135,7 +3272,7 @@
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="26" t="str">
-        <f aca="false">IF(D9&gt;0,E9/D9*100,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G9" s="13"/>
@@ -3143,12 +3280,12 @@
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="18" t="str">
-        <f aca="false">IF(F9="","",IF(AND(F9&gt;=90,F9&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>106</v>
       </c>
@@ -3157,7 +3294,7 @@
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="25" t="str">
-        <f aca="false">IF(D10&gt;0,E10/D10*100,"")</f>
+        <f t="shared" ref="F10:F28" si="6">IF(D10&gt;0,E10/D10*100,"")</f>
         <v/>
       </c>
       <c r="G10" s="13"/>
@@ -3165,12 +3302,12 @@
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15" t="str">
-        <f aca="false">IF(F10="","",IF(AND(F10&gt;=90,F10&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K10:K27" si="7">IF(F10="","",IF(AND(F10&gt;=90,F10&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>107</v>
       </c>
@@ -3179,7 +3316,7 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="26" t="str">
-        <f aca="false">IF(D11&gt;0,E11/D11*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G11" s="13"/>
@@ -3187,12 +3324,12 @@
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="18" t="str">
-        <f aca="false">IF(F11="","",IF(AND(F11&gt;=90,F11&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>108</v>
       </c>
@@ -3201,7 +3338,7 @@
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="25" t="str">
-        <f aca="false">IF(D12&gt;0,E12/D12*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G12" s="13"/>
@@ -3209,12 +3346,12 @@
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
       <c r="K12" s="15" t="str">
-        <f aca="false">IF(F12="","",IF(AND(F12&gt;=90,F12&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>109</v>
       </c>
@@ -3223,7 +3360,7 @@
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="26" t="str">
-        <f aca="false">IF(D13&gt;0,E13/D13*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G13" s="13"/>
@@ -3231,12 +3368,12 @@
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="K13" s="18" t="str">
-        <f aca="false">IF(F13="","",IF(AND(F13&gt;=90,F13&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L13" s="26"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>110</v>
       </c>
@@ -3245,7 +3382,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="25" t="str">
-        <f aca="false">IF(D14&gt;0,E14/D14*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G14" s="13"/>
@@ -3253,12 +3390,12 @@
       <c r="I14" s="25"/>
       <c r="J14" s="25"/>
       <c r="K14" s="15" t="str">
-        <f aca="false">IF(F14="","",IF(AND(F14&gt;=90,F14&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L14" s="25"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>111</v>
       </c>
@@ -3267,7 +3404,7 @@
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="26" t="str">
-        <f aca="false">IF(D15&gt;0,E15/D15*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G15" s="13"/>
@@ -3275,27 +3412,27 @@
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="18" t="str">
-        <f aca="false">IF(F15="","",IF(AND(F15&gt;=90,F15&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="27" t="s">
         <v>112</v>
       </c>
       <c r="B16" s="27"/>
       <c r="C16" s="27"/>
-      <c r="D16" s="27" t="n">
-        <f aca="false">SUM(D4:D15)</f>
+      <c r="D16" s="27">
+        <f>SUM(D4:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="27" t="n">
-        <f aca="false">SUM(E4:E15)</f>
+      <c r="E16" s="27">
+        <f>SUM(E4:E15)</f>
         <v>0</v>
       </c>
       <c r="F16" s="27" t="str">
-        <f aca="false">IF(D16&gt;0,E16/D16*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G16" s="27"/>
@@ -3305,8 +3442,8 @@
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
     </row>
-    <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="7.5" customHeight="1"/>
+    <row r="18" ht="21.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>113</v>
       </c>
@@ -3321,10 +3458,8 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>114</v>
       </c>
@@ -3362,7 +3497,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12" t="s">
         <v>120</v>
       </c>
@@ -3371,7 +3506,7 @@
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="25" t="str">
-        <f aca="false">IF(D20&gt;0,E20/D20*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G20" s="13"/>
@@ -3379,12 +3514,12 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="15" t="str">
-        <f aca="false">IF(F20="","",IF(AND(F20&gt;=90,F20&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>121</v>
       </c>
@@ -3393,7 +3528,7 @@
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="26" t="str">
-        <f aca="false">IF(D21&gt;0,E21/D21*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G21" s="13"/>
@@ -3401,12 +3536,12 @@
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(AND(F21&gt;=90,F21&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="12" t="s">
         <v>122</v>
       </c>
@@ -3415,7 +3550,7 @@
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="25" t="str">
-        <f aca="false">IF(D22&gt;0,E22/D22*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G22" s="13"/>
@@ -3423,12 +3558,12 @@
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="15" t="str">
-        <f aca="false">IF(F22="","",IF(AND(F22&gt;=90,F22&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
         <v>123</v>
       </c>
@@ -3437,7 +3572,7 @@
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="26" t="str">
-        <f aca="false">IF(D23&gt;0,E23/D23*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G23" s="13"/>
@@ -3445,12 +3580,12 @@
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(AND(F23&gt;=90,F23&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L23" s="26"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12" t="s">
         <v>124</v>
       </c>
@@ -3459,7 +3594,7 @@
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="25" t="str">
-        <f aca="false">IF(D24&gt;0,E24/D24*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G24" s="13"/>
@@ -3467,12 +3602,12 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="15" t="str">
-        <f aca="false">IF(F24="","",IF(AND(F24&gt;=90,F24&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="16" t="s">
         <v>125</v>
       </c>
@@ -3481,7 +3616,7 @@
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="26" t="str">
-        <f aca="false">IF(D25&gt;0,E25/D25*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G25" s="13"/>
@@ -3489,12 +3624,12 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(AND(F25&gt;=90,F25&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L25" s="26"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="s">
         <v>126</v>
       </c>
@@ -3503,7 +3638,7 @@
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="25" t="str">
-        <f aca="false">IF(D26&gt;0,E26/D26*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G26" s="13"/>
@@ -3511,12 +3646,12 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="15" t="str">
-        <f aca="false">IF(F26="","",IF(AND(F26&gt;=90,F26&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>127</v>
       </c>
@@ -3525,7 +3660,7 @@
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="26" t="str">
-        <f aca="false">IF(D27&gt;0,E27/D27*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G27" s="13"/>
@@ -3533,27 +3668,27 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="18" t="str">
-        <f aca="false">IF(F27="","",IF(AND(F27&gt;=90,F27&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L27" s="26"/>
     </row>
-    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="16.5" customHeight="1">
       <c r="A28" s="27" t="s">
         <v>128</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
-      <c r="D28" s="27" t="n">
-        <f aca="false">SUM(D20:D27)</f>
+      <c r="D28" s="27">
+        <f>SUM(D20:D27)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="27" t="n">
-        <f aca="false">SUM(E20:E27)</f>
+      <c r="E28" s="27">
+        <f>SUM(E20:E27)</f>
         <v>0</v>
       </c>
       <c r="F28" s="27" t="str">
-        <f aca="false">IF(D28&gt;0,E28/D28*100,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="G28" s="27"/>
@@ -3563,22 +3698,22 @@
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+    <row r="29" ht="4.5" customHeight="1"/>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3588,48 +3723,45 @@
     <mergeCell ref="A18:L18"/>
     <mergeCell ref="A30:L30"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="26"/>
+    <col customWidth="1" min="2" max="3" style="0" width="16"/>
+    <col customWidth="1" min="4" max="6" style="0" width="14"/>
+    <col customWidth="1" min="7" max="7" style="0" width="10"/>
+    <col customWidth="1" min="8" max="8" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>129</v>
       </c>
@@ -3640,13 +3772,13 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>130</v>
       </c>
@@ -3670,8 +3802,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>135</v>
       </c>
       <c r="B4" s="13"/>
@@ -3686,8 +3818,8 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B5" s="13"/>
@@ -3702,8 +3834,8 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>138</v>
       </c>
       <c r="B6" s="13"/>
@@ -3718,8 +3850,8 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>139</v>
       </c>
       <c r="B7" s="13"/>
@@ -3734,8 +3866,8 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B8" s="13"/>
@@ -3750,8 +3882,8 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>143</v>
       </c>
       <c r="B9" s="13"/>
@@ -3766,8 +3898,8 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>144</v>
       </c>
       <c r="B10" s="13"/>
@@ -3782,8 +3914,8 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B11" s="13"/>
@@ -3798,8 +3930,8 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B12" s="13"/>
@@ -3812,8 +3944,8 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>150</v>
       </c>
       <c r="B13" s="13"/>
@@ -3828,8 +3960,8 @@
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>152</v>
       </c>
       <c r="B14" s="13"/>
@@ -3842,8 +3974,8 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B15" s="13"/>
@@ -3854,8 +3986,8 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B16" s="13"/>
@@ -3868,8 +4000,8 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B17" s="13"/>
@@ -3882,8 +4014,8 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B18" s="13"/>
@@ -3896,8 +4028,8 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B19" s="13"/>
@@ -3910,8 +4042,8 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B20" s="13"/>
@@ -3924,8 +4056,8 @@
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="s">
         <v>161</v>
       </c>
       <c r="B21" s="13"/>
@@ -3940,8 +4072,8 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="5" t="s">
         <v>163</v>
       </c>
       <c r="B22" s="13"/>
@@ -3952,8 +4084,8 @@
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B23" s="13"/>
@@ -3966,8 +4098,8 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B24" s="13"/>
@@ -3980,8 +4112,8 @@
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B25" s="13"/>
@@ -3994,8 +4126,8 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="4.5" customHeight="1"/>
+    <row r="27" ht="21.75" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>168</v>
       </c>
@@ -4006,14 +4138,14 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>169</v>
       </c>
@@ -4037,8 +4169,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="5" t="s">
         <v>173</v>
       </c>
       <c r="B29" s="13"/>
@@ -4051,8 +4183,8 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="5" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="13"/>
@@ -4065,8 +4197,8 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="5" t="s">
         <v>175</v>
       </c>
       <c r="B31" s="13"/>
@@ -4079,8 +4211,8 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B32" s="13"/>
@@ -4093,8 +4225,8 @@
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>177</v>
       </c>
       <c r="B33" s="13"/>
@@ -4107,8 +4239,8 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="13"/>
@@ -4121,8 +4253,8 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="5" t="s">
         <v>179</v>
       </c>
       <c r="B35" s="13"/>
@@ -4135,8 +4267,8 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="5" t="s">
         <v>180</v>
       </c>
       <c r="B36" s="13"/>
@@ -4149,8 +4281,8 @@
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="5" t="s">
         <v>181</v>
       </c>
       <c r="B37" s="13"/>
@@ -4163,8 +4295,8 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B38" s="13"/>
@@ -4177,18 +4309,18 @@
       <c r="G38" s="16"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
+    <row r="39" ht="4.5" customHeight="1"/>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
       <c r="I40" s="24"/>
       <c r="J40" s="24"/>
       <c r="K40" s="24"/>
@@ -4202,33 +4334,30 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="20"/>
+    <col customWidth="1" min="2" max="7" style="0" width="12"/>
+    <col customWidth="1" min="8" max="8" style="0" width="14"/>
+    <col customWidth="1" min="9" max="10" style="0" width="12"/>
+    <col customWidth="1" min="11" max="11" style="0" width="10"/>
+    <col customWidth="1" min="12" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4237,14 +4366,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>183</v>
       </c>
@@ -4259,9 +4388,9 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>184</v>
       </c>
@@ -4299,7 +4428,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>193</v>
       </c>
@@ -4309,22 +4438,22 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="12" t="str">
-        <f aca="false">IF(C4&gt;0,E4*C4,"")</f>
+        <f t="shared" ref="G4:G9" si="8">IF(C4&gt;0,E4*C4,"")</f>
         <v/>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="12" t="str">
-        <f aca="false">IF(H4&lt;&gt;"",H4-I4,"")</f>
+        <f t="shared" ref="J4:J9" si="9">IF(H4&lt;&gt;"",H4-I4,"")</f>
         <v/>
       </c>
       <c r="K4" s="15" t="str">
-        <f aca="false">IF(F4="","",IF(AND(G4&gt;=F4*0.9,G4&lt;=F4*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K4:K9" si="10">IF(F4="","",IF(AND(G4&gt;=F4*0.9,G4&lt;=F4*1.1),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L4" s="25"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>194</v>
       </c>
@@ -4334,22 +4463,22 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="16" t="str">
-        <f aca="false">IF(C5&gt;0,E5*C5,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="16" t="str">
-        <f aca="false">IF(H5&lt;&gt;"",H5-I5,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K5" s="18" t="str">
-        <f aca="false">IF(F5="","",IF(AND(G5&gt;=F5*0.9,G5&lt;=F5*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>195</v>
       </c>
@@ -4359,22 +4488,22 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="12" t="str">
-        <f aca="false">IF(C6&gt;0,E6*C6,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="12" t="str">
-        <f aca="false">IF(H6&lt;&gt;"",H6-I6,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K6" s="15" t="str">
-        <f aca="false">IF(F6="","",IF(AND(G6&gt;=F6*0.9,G6&lt;=F6*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>196</v>
       </c>
@@ -4384,22 +4513,22 @@
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="16" t="str">
-        <f aca="false">IF(C7&gt;0,E7*C7,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="16" t="str">
-        <f aca="false">IF(H7&lt;&gt;"",H7-I7,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K7" s="18" t="str">
-        <f aca="false">IF(F7="","",IF(AND(G7&gt;=F7*0.9,G7&lt;=F7*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="L7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>197</v>
       </c>
@@ -4409,22 +4538,22 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="12" t="str">
-        <f aca="false">IF(C8&gt;0,E8*C8,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="12" t="str">
-        <f aca="false">IF(H8&lt;&gt;"",H8-I8,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K8" s="15" t="str">
-        <f aca="false">IF(F8="","",IF(AND(G8&gt;=F8*0.9,G8&lt;=F8*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="L8" s="25"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>198</v>
       </c>
@@ -4434,22 +4563,22 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="16" t="str">
-        <f aca="false">IF(C9&gt;0,E9*C9,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="16" t="str">
-        <f aca="false">IF(H9&lt;&gt;"",H9-I9,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K9" s="18" t="str">
-        <f aca="false">IF(F9="","",IF(AND(G9&gt;=F9*0.9,G9&lt;=F9*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>199</v>
       </c>
@@ -4459,22 +4588,22 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="12" t="str">
-        <f aca="false">IF(C10&gt;0,E10*C10,"")</f>
+        <f t="shared" ref="G10:G18" si="11">IF(C10&gt;0,E10*C10,"")</f>
         <v/>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="12" t="str">
-        <f aca="false">IF(H10&lt;&gt;"",H10-I10,"")</f>
+        <f t="shared" ref="J10:J18" si="12">IF(H10&lt;&gt;"",H10-I10,"")</f>
         <v/>
       </c>
       <c r="K10" s="15" t="str">
-        <f aca="false">IF(F10="","",IF(AND(G10&gt;=F10*0.9,G10&lt;=F10*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K10:K18" si="13">IF(F10="","",IF(AND(G10&gt;=F10*0.9,G10&lt;=F10*1.1),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>200</v>
       </c>
@@ -4484,22 +4613,22 @@
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="16" t="str">
-        <f aca="false">IF(C11&gt;0,E11*C11,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="16" t="str">
-        <f aca="false">IF(H11&lt;&gt;"",H11-I11,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K11" s="18" t="str">
-        <f aca="false">IF(F11="","",IF(AND(G11&gt;=F11*0.9,G11&lt;=F11*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>201</v>
       </c>
@@ -4509,22 +4638,22 @@
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="str">
-        <f aca="false">IF(C12&gt;0,E12*C12,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="12" t="str">
-        <f aca="false">IF(H12&lt;&gt;"",H12-I12,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K12" s="15" t="str">
-        <f aca="false">IF(F12="","",IF(AND(G12&gt;=F12*0.9,G12&lt;=F12*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>202</v>
       </c>
@@ -4534,22 +4663,22 @@
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="16" t="str">
-        <f aca="false">IF(C13&gt;0,E13*C13,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="16" t="str">
-        <f aca="false">IF(H13&lt;&gt;"",H13-I13,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K13" s="18" t="str">
-        <f aca="false">IF(F13="","",IF(AND(G13&gt;=F13*0.9,G13&lt;=F13*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L13" s="26"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>203</v>
       </c>
@@ -4559,22 +4688,22 @@
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="12" t="str">
-        <f aca="false">IF(C14&gt;0,E14*C14,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="12" t="str">
-        <f aca="false">IF(H14&lt;&gt;"",H14-I14,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K14" s="15" t="str">
-        <f aca="false">IF(F14="","",IF(AND(G14&gt;=F14*0.9,G14&lt;=F14*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L14" s="25"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>204</v>
       </c>
@@ -4584,22 +4713,22 @@
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
       <c r="G15" s="16" t="str">
-        <f aca="false">IF(C15&gt;0,E15*C15,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="16" t="str">
-        <f aca="false">IF(H15&lt;&gt;"",H15-I15,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K15" s="18" t="str">
-        <f aca="false">IF(F15="","",IF(AND(G15&gt;=F15*0.9,G15&lt;=F15*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="s">
         <v>205</v>
       </c>
@@ -4609,22 +4738,22 @@
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="12" t="str">
-        <f aca="false">IF(C16&gt;0,E16*C16,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="12" t="str">
-        <f aca="false">IF(H16&lt;&gt;"",H16-I16,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K16" s="15" t="str">
-        <f aca="false">IF(F16="","",IF(AND(G16&gt;=F16*0.9,G16&lt;=F16*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="s">
         <v>206</v>
       </c>
@@ -4634,22 +4763,22 @@
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="16" t="str">
-        <f aca="false">IF(C17&gt;0,E17*C17,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="16" t="str">
-        <f aca="false">IF(H17&lt;&gt;"",H17-I17,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(AND(G17&gt;=F17*0.9,G17&lt;=F17*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L17" s="26"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="s">
         <v>207</v>
       </c>
@@ -4659,37 +4788,37 @@
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="12" t="str">
-        <f aca="false">IF(C18&gt;0,E18*C18,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="12" t="str">
-        <f aca="false">IF(H18&lt;&gt;"",H18-I18,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K18" s="15" t="str">
-        <f aca="false">IF(F18="","",IF(AND(G18&gt;=F18*0.9,G18&lt;=F18*1.1),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+    <row r="19" ht="4.5" customHeight="1"/>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4698,34 +4827,31 @@
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A20:L20"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="20"/>
+    <col customWidth="1" min="2" max="2" style="0" width="14"/>
+    <col customWidth="1" min="3" max="8" style="0" width="12"/>
+    <col customWidth="1" min="9" max="9" style="0" width="10"/>
+    <col customWidth="1" min="10" max="10" style="0" width="12"/>
+    <col customWidth="1" min="11" max="11" style="0" width="10"/>
+    <col customWidth="1" min="12" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4734,14 +4860,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>208</v>
       </c>
@@ -4756,9 +4882,9 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>209</v>
       </c>
@@ -4796,7 +4922,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>217</v>
       </c>
@@ -4804,24 +4930,24 @@
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="25" t="str">
-        <f aca="false">IF(C4&gt;0,D4/C4*100,"")</f>
+        <f t="shared" ref="E4:E9" si="14">IF(C4&gt;0,D4/C4*100,"")</f>
         <v/>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="25" t="str">
-        <f aca="false">IF(G4&lt;&gt;"",G4-F4,"")</f>
+        <f t="shared" ref="H4:H9" si="15">IF(G4&lt;&gt;"",G4-F4,"")</f>
         <v/>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
       <c r="K4" s="15" t="str">
-        <f aca="false">IF(C4="","",IF(AND(E4&gt;=90,E4&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K4:K9" si="16">IF(C4="","",IF(AND(E4&gt;=90,E4&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L4" s="25"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>218</v>
       </c>
@@ -4829,24 +4955,24 @@
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="26" t="str">
-        <f aca="false">IF(C5&gt;0,D5/C5*100,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="26" t="str">
-        <f aca="false">IF(G5&lt;&gt;"",G5-F5,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="18" t="str">
-        <f aca="false">IF(C5="","",IF(AND(E5&gt;=90,E5&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>219</v>
       </c>
@@ -4854,24 +4980,24 @@
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="25" t="str">
-        <f aca="false">IF(C6&gt;0,D6/C6*100,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="25" t="str">
-        <f aca="false">IF(G6&lt;&gt;"",G6-F6,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="15" t="str">
-        <f aca="false">IF(C6="","",IF(AND(E6&gt;=90,E6&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>220</v>
       </c>
@@ -4879,24 +5005,24 @@
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="26" t="str">
-        <f aca="false">IF(C7&gt;0,D7/C7*100,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="26" t="str">
-        <f aca="false">IF(G7&lt;&gt;"",G7-F7,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="18" t="str">
-        <f aca="false">IF(C7="","",IF(AND(E7&gt;=90,E7&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>221</v>
       </c>
@@ -4904,24 +5030,24 @@
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="25" t="str">
-        <f aca="false">IF(C8&gt;0,D8/C8*100,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="25" t="str">
-        <f aca="false">IF(G8&lt;&gt;"",G8-F8,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="15" t="str">
-        <f aca="false">IF(C8="","",IF(AND(E8&gt;=90,E8&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L8" s="25"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>222</v>
       </c>
@@ -4929,24 +5055,24 @@
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="26" t="str">
-        <f aca="false">IF(C9&gt;0,D9/C9*100,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="26" t="str">
-        <f aca="false">IF(G9&lt;&gt;"",G9-F9,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="18" t="str">
-        <f aca="false">IF(C9="","",IF(AND(E9&gt;=90,E9&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>223</v>
       </c>
@@ -4954,24 +5080,24 @@
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="25" t="str">
-        <f aca="false">IF(C10&gt;0,D10/C10*100,"")</f>
+        <f t="shared" ref="E10:E20" si="17">IF(C10&gt;0,D10/C10*100,"")</f>
         <v/>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="25" t="str">
-        <f aca="false">IF(G10&lt;&gt;"",G10-F10,"")</f>
+        <f t="shared" ref="H10:H19" si="18">IF(G10&lt;&gt;"",G10-F10,"")</f>
         <v/>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="15" t="str">
-        <f aca="false">IF(C10="","",IF(AND(E10&gt;=90,E10&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" ref="K10:K19" si="19">IF(C10="","",IF(AND(E10&gt;=90,E10&lt;=110),"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>224</v>
       </c>
@@ -4979,24 +5105,24 @@
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="26" t="str">
-        <f aca="false">IF(C11&gt;0,D11/C11*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="26" t="str">
-        <f aca="false">IF(G11&lt;&gt;"",G11-F11,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="K11" s="18" t="str">
-        <f aca="false">IF(C11="","",IF(AND(E11&gt;=90,E11&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>225</v>
       </c>
@@ -5004,24 +5130,24 @@
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="25" t="str">
-        <f aca="false">IF(C12&gt;0,D12/C12*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="25" t="str">
-        <f aca="false">IF(G12&lt;&gt;"",G12-F12,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="15" t="str">
-        <f aca="false">IF(C12="","",IF(AND(E12&gt;=90,E12&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>226</v>
       </c>
@@ -5029,24 +5155,24 @@
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="26" t="str">
-        <f aca="false">IF(C13&gt;0,D13/C13*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="26" t="str">
-        <f aca="false">IF(G13&lt;&gt;"",G13-F13,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="18" t="str">
-        <f aca="false">IF(C13="","",IF(AND(E13&gt;=90,E13&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L13" s="26"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>227</v>
       </c>
@@ -5054,24 +5180,24 @@
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="25" t="str">
-        <f aca="false">IF(C14&gt;0,D14/C14*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="25" t="str">
-        <f aca="false">IF(G14&lt;&gt;"",G14-F14,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="15" t="str">
-        <f aca="false">IF(C14="","",IF(AND(E14&gt;=90,E14&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L14" s="25"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>228</v>
       </c>
@@ -5079,24 +5205,24 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="26" t="str">
-        <f aca="false">IF(C15&gt;0,D15/C15*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="26" t="str">
-        <f aca="false">IF(G15&lt;&gt;"",G15-F15,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="18" t="str">
-        <f aca="false">IF(C15="","",IF(AND(E15&gt;=90,E15&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="s">
         <v>229</v>
       </c>
@@ -5104,24 +5230,24 @@
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="25" t="str">
-        <f aca="false">IF(C16&gt;0,D16/C16*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="25" t="str">
-        <f aca="false">IF(G16&lt;&gt;"",G16-F16,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="15" t="str">
-        <f aca="false">IF(C16="","",IF(AND(E16&gt;=90,E16&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="s">
         <v>230</v>
       </c>
@@ -5129,24 +5255,24 @@
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="26" t="str">
-        <f aca="false">IF(C17&gt;0,D17/C17*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="26" t="str">
-        <f aca="false">IF(G17&lt;&gt;"",G17-F17,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="18" t="str">
-        <f aca="false">IF(C17="","",IF(AND(E17&gt;=90,E17&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L17" s="26"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="s">
         <v>231</v>
       </c>
@@ -5154,24 +5280,24 @@
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="25" t="str">
-        <f aca="false">IF(C18&gt;0,D18/C18*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="25" t="str">
-        <f aca="false">IF(G18&lt;&gt;"",G18-F18,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="15" t="str">
-        <f aca="false">IF(C18="","",IF(AND(E18&gt;=90,E18&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
         <v>232</v>
       </c>
@@ -5179,38 +5305,38 @@
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="26" t="str">
-        <f aca="false">IF(C19&gt;0,D19/C19*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="26" t="str">
-        <f aca="false">IF(G19&lt;&gt;"",G19-F19,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="18" t="str">
-        <f aca="false">IF(C19="","",IF(AND(E19&gt;=90,E19&lt;=110),"✓ PASS","✗ FAIL"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L19" s="26"/>
     </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="19" t="s">
         <v>87</v>
       </c>
       <c r="B20" s="19"/>
-      <c r="C20" s="19" t="n">
-        <f aca="false">SUM(C4:C19)</f>
+      <c r="C20" s="19">
+        <f>SUM(C4:C19)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="19" t="n">
-        <f aca="false">SUM(D4:D19)</f>
+      <c r="D20" s="19">
+        <f>SUM(D4:D19)</f>
         <v>0</v>
       </c>
       <c r="E20" s="19" t="str">
-        <f aca="false">IF(C20&gt;0,D20/C20*100,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F20" s="19"/>
@@ -5221,22 +5347,22 @@
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+    <row r="21" ht="4.5" customHeight="1"/>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5245,49 +5371,46 @@
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A22:L22"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col customWidth="1" min="1" max="1" style="0" width="40"/>
+    <col customWidth="1" min="2" max="3" style="0" width="10"/>
+    <col customWidth="1" min="4" max="4" style="0" width="8"/>
+    <col customWidth="1" min="5" max="5" style="0" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>233</v>
       </c>
@@ -5295,16 +5418,16 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>234</v>
       </c>
@@ -5321,7 +5444,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="28" t="s">
         <v>239</v>
       </c>
@@ -5330,7 +5453,7 @@
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="29" t="s">
         <v>240</v>
       </c>
@@ -5343,9 +5466,9 @@
       <c r="D5" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>242</v>
       </c>
@@ -5358,9 +5481,9 @@
       <c r="D6" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="29" t="s">
         <v>243</v>
       </c>
@@ -5373,9 +5496,9 @@
       <c r="D7" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>244</v>
       </c>
@@ -5388,9 +5511,9 @@
       <c r="D8" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="29" t="s">
         <v>245</v>
       </c>
@@ -5403,9 +5526,9 @@
       <c r="D9" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>246</v>
       </c>
@@ -5418,9 +5541,9 @@
       <c r="D10" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="29" t="s">
         <v>247</v>
       </c>
@@ -5433,9 +5556,9 @@
       <c r="D11" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="s">
         <v>248</v>
       </c>
@@ -5448,9 +5571,9 @@
       <c r="D12" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="29" t="s">
         <v>249</v>
       </c>
@@ -5463,9 +5586,9 @@
       <c r="D13" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="s">
         <v>250</v>
       </c>
@@ -5478,9 +5601,9 @@
       <c r="D14" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="29" t="s">
         <v>251</v>
       </c>
@@ -5493,9 +5616,9 @@
       <c r="D15" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="s">
         <v>252</v>
       </c>
@@ -5508,10 +5631,10 @@
       <c r="D16" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" ht="3.75" customHeight="1"/>
+    <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="28" t="s">
         <v>253</v>
       </c>
@@ -5520,7 +5643,7 @@
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="29" t="s">
         <v>254</v>
       </c>
@@ -5533,9 +5656,9 @@
       <c r="D19" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="s">
         <v>255</v>
       </c>
@@ -5548,9 +5671,9 @@
       <c r="D20" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="29" t="s">
         <v>256</v>
       </c>
@@ -5563,9 +5686,9 @@
       <c r="D21" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="s">
         <v>257</v>
       </c>
@@ -5578,9 +5701,9 @@
       <c r="D22" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="29" t="s">
         <v>258</v>
       </c>
@@ -5593,9 +5716,9 @@
       <c r="D23" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="s">
         <v>259</v>
       </c>
@@ -5608,10 +5731,10 @@
       <c r="D24" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" ht="3.75" customHeight="1"/>
+    <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="28" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5743,7 @@
       <c r="D26" s="28"/>
       <c r="E26" s="28"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="29" t="s">
         <v>261</v>
       </c>
@@ -5633,9 +5756,9 @@
       <c r="D27" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="s">
         <v>262</v>
       </c>
@@ -5648,9 +5771,9 @@
       <c r="D28" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="29" t="s">
         <v>263</v>
       </c>
@@ -5663,9 +5786,9 @@
       <c r="D29" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="s">
         <v>264</v>
       </c>
@@ -5678,9 +5801,9 @@
       <c r="D30" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="29" t="s">
         <v>265</v>
       </c>
@@ -5693,9 +5816,9 @@
       <c r="D31" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="s">
         <v>266</v>
       </c>
@@ -5708,9 +5831,9 @@
       <c r="D32" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="29" t="s">
         <v>267</v>
       </c>
@@ -5723,10 +5846,10 @@
       <c r="D33" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" ht="3.75" customHeight="1"/>
+    <row r="35" ht="16.5" customHeight="1">
       <c r="A35" s="28" t="s">
         <v>268</v>
       </c>
@@ -5735,7 +5858,7 @@
       <c r="D35" s="28"/>
       <c r="E35" s="28"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="29" t="s">
         <v>269</v>
       </c>
@@ -5748,9 +5871,9 @@
       <c r="D36" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E36" s="8"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="31" t="s">
         <v>270</v>
       </c>
@@ -5763,9 +5886,9 @@
       <c r="D37" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="29" t="s">
         <v>271</v>
       </c>
@@ -5778,9 +5901,9 @@
       <c r="D38" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="31" t="s">
         <v>272</v>
       </c>
@@ -5793,9 +5916,9 @@
       <c r="D39" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="29" t="s">
         <v>273</v>
       </c>
@@ -5808,9 +5931,9 @@
       <c r="D40" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E40" s="8"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="31" t="s">
         <v>274</v>
       </c>
@@ -5823,9 +5946,9 @@
       <c r="D41" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E41" s="8"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="29" t="s">
         <v>275</v>
       </c>
@@ -5838,9 +5961,9 @@
       <c r="D42" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
       <c r="A43" s="31" t="s">
         <v>276</v>
       </c>
@@ -5853,9 +5976,9 @@
       <c r="D43" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E43" s="8"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="29" t="s">
         <v>277</v>
       </c>
@@ -5868,9 +5991,9 @@
       <c r="D44" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E44" s="8"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="31" t="s">
         <v>278</v>
       </c>
@@ -5883,17 +6006,17 @@
       <c r="D45" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="E45" s="8"/>
-    </row>
-    <row r="46" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" ht="3.75" customHeight="1"/>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="24"/>
       <c r="G47" s="24"/>
       <c r="H47" s="24"/>
@@ -5909,50 +6032,47 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A47:E47"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col customWidth="1" min="1" max="1" style="0" width="8"/>
+    <col customWidth="1" min="2" max="2" style="0" width="18"/>
+    <col customWidth="1" min="3" max="3" style="0" width="28"/>
+    <col customWidth="1" min="4" max="4" style="0" width="18"/>
+    <col customWidth="1" min="5" max="6" style="0" width="12"/>
+    <col customWidth="1" min="7" max="7" style="0" width="14"/>
+    <col customWidth="1" min="8" max="8" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>279</v>
       </c>
@@ -5963,13 +6083,13 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>280</v>
       </c>
@@ -5995,11 +6115,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="n">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="25">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
       <c r="E4" s="13"/>
@@ -6007,11 +6127,11 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="n">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="26">
         <v>2</v>
       </c>
-      <c r="B5" s="7"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="E5" s="13"/>
@@ -6019,11 +6139,11 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="n">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="13"/>
@@ -6031,11 +6151,11 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="26">
         <v>4</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="13"/>
@@ -6043,11 +6163,11 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="25">
         <v>5</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="E8" s="13"/>
@@ -6055,11 +6175,11 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="n">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="26">
         <v>6</v>
       </c>
-      <c r="B9" s="7"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="E9" s="13"/>
@@ -6067,11 +6187,11 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="25">
         <v>7</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="E10" s="13"/>
@@ -6079,11 +6199,11 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="n">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="26">
         <v>8</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="13"/>
@@ -6091,11 +6211,11 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="25">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="13"/>
@@ -6103,11 +6223,11 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="n">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="26">
         <v>10</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
       <c r="E13" s="13"/>
@@ -6115,11 +6235,11 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="n">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="25">
         <v>11</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="13"/>
@@ -6127,11 +6247,11 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="n">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="26">
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="13"/>
@@ -6139,11 +6259,11 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="n">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="25">
         <v>13</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="13"/>
@@ -6151,11 +6271,11 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26">
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
       <c r="E17" s="13"/>
@@ -6163,11 +6283,11 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="n">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="25">
         <v>15</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="13"/>
@@ -6175,11 +6295,11 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="n">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="26">
         <v>16</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
       <c r="E19" s="13"/>
@@ -6187,11 +6307,11 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="n">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="25">
         <v>17</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
       <c r="E20" s="13"/>
@@ -6199,11 +6319,11 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="n">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="26">
         <v>18</v>
       </c>
-      <c r="B21" s="7"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="13"/>
@@ -6211,11 +6331,11 @@
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="n">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="25">
         <v>19</v>
       </c>
-      <c r="B22" s="7"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
       <c r="E22" s="13"/>
@@ -6223,11 +6343,11 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="n">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="26">
         <v>20</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
       <c r="E23" s="13"/>
@@ -6235,8 +6355,8 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="24" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="4.5" customHeight="1"/>
+    <row r="25" ht="21.75" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>287</v>
       </c>
@@ -6247,85 +6367,85 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="21" t="n">
-        <f aca="false">COUNTA(B4:B23)</f>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="21">
+        <f>COUNTA(B4:B23)</f>
         <v>0</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="21" t="n">
-        <f aca="false">COUNTIF(H4:H23,"Open")</f>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="21">
+        <f>COUNTIF(H4:H23,"Open")</f>
         <v>0</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="21" t="n">
-        <f aca="false">COUNTIF(H4:H23,"Closed")</f>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="21">
+        <f>COUNTIF(H4:H23,"Closed")</f>
         <v>0</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="21" t="n">
-        <f aca="false">COUNTIF(H4:H23,"Critical")</f>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="21">
+        <f>COUNTIF(H4:H23,"Critical")</f>
         <v>0</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+    <row r="30" ht="4.5" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
       <c r="I31" s="24"/>
       <c r="J31" s="24"/>
       <c r="K31" s="24"/>
@@ -6347,29 +6467,26 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="14"/>
+    <col customWidth="1" min="1" max="1" style="0" width="22"/>
+    <col customWidth="1" min="2" max="12" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6378,15 +6495,15 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" ht="7.5" customHeight="1"/>
+    <row r="3" ht="27.75" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>292</v>
       </c>
@@ -6402,8 +6519,8 @@
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
     </row>
-    <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="4.5" customHeight="1"/>
+    <row r="5" ht="21.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>293</v>
       </c>
@@ -6418,9 +6535,8 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>294</v>
       </c>
@@ -6450,8 +6566,8 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>297</v>
       </c>
       <c r="B7" s="13"/>
@@ -6466,8 +6582,8 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>298</v>
       </c>
       <c r="B8" s="13"/>
@@ -6482,8 +6598,8 @@
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>299</v>
       </c>
       <c r="B9" s="13"/>
@@ -6498,8 +6614,8 @@
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>300</v>
       </c>
       <c r="B10" s="13"/>
@@ -6514,8 +6630,8 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>301</v>
       </c>
       <c r="B11" s="13"/>
@@ -6530,8 +6646,8 @@
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
     </row>
-    <row r="12" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="4.5" customHeight="1"/>
+    <row r="13" ht="21.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>302</v>
       </c>
@@ -6546,107 +6662,105 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" ht="4.5" customHeight="1"/>
+    <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>309</v>
       </c>
@@ -6661,11 +6775,8 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -6679,7 +6790,7 @@
       <c r="K22" s="34"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="34"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -6693,7 +6804,7 @@
       <c r="K23" s="34"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="34"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -6707,7 +6818,7 @@
       <c r="K24" s="34"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="34"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -6721,7 +6832,7 @@
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="34"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
@@ -6735,7 +6846,7 @@
       <c r="K26" s="34"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -6749,7 +6860,7 @@
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -6763,7 +6874,7 @@
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="34"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -6777,8 +6888,8 @@
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
     </row>
-    <row r="30" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="4.5" customHeight="1"/>
+    <row r="31" ht="21.75" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>310</v>
       </c>
@@ -6793,115 +6904,111 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="6" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="6" t="s">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="6" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="6" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="6" t="s">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="6" t="s">
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="6" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="6" t="s">
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="6" t="s">
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="6" t="s">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="6" t="s">
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="6" t="s">
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+    </row>
+    <row r="36" ht="4.5" customHeight="1"/>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -6934,12 +7041,9 @@
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A37:L37"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>